--- a/SQExcel.Portal/src/content/docs/ja/docs/images/option-settings-dialog/option-settings-dialog.xlsx
+++ b/SQExcel.Portal/src/content/docs/ja/docs/images/option-settings-dialog/option-settings-dialog.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos_MS\East\SQL2Excel\v100\SQL2Excel\SQL2Excel.Help\src\content\docs\ja\images\option-settings-dialog\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos_GitEms\sqexcel\SQExcel.Portal\src\content\docs\ja\docs\images\option-settings-dialog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83564BC6-310A-49EC-8965-52E35162DEE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10441765-D95F-40F7-9289-FF8A3333C259}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="950" yWindow="850" windowWidth="21910" windowHeight="12980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1536" yWindow="1536" windowWidth="16680" windowHeight="12072" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="option-settings-dialog" sheetId="3" r:id="rId1"/>
@@ -1643,1487 +1643,6 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>231587</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>216647</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>2745291</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>148091</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{38322839-826B-DCA2-2B93-6D1E32875A01}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="463175" y="2069353"/>
-          <a:ext cx="8520057" cy="3173679"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>234790</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>18143</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>2748494</xdr:colOff>
-      <xdr:row>57</xdr:row>
-      <xdr:rowOff>95906</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="19" name="グループ化 18">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FA50BCC8-2454-350D-91C4-3142E4A93BAC}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="466378" y="6502614"/>
-          <a:ext cx="8520057" cy="6793821"/>
-          <a:chOff x="451597" y="6858001"/>
-          <a:chExt cx="8644442" cy="6707163"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:grpSp>
-        <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="10" name="グループ化 9">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F9C3B10C-11A3-2DA9-9315-B4A472E94991}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvGrpSpPr/>
-        </xdr:nvGrpSpPr>
-        <xdr:grpSpPr>
-          <a:xfrm>
-            <a:off x="451597" y="6858001"/>
-            <a:ext cx="8644442" cy="6707163"/>
-            <a:chOff x="451597" y="6858001"/>
-            <a:chExt cx="8644442" cy="6707163"/>
-          </a:xfrm>
-        </xdr:grpSpPr>
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="4" name="図 3">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5692D72E-F8A2-7504-97D3-F475AD699425}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvPicPr>
-              <a:picLocks noChangeAspect="1"/>
-            </xdr:cNvPicPr>
-          </xdr:nvPicPr>
-          <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-            <a:stretch>
-              <a:fillRect/>
-            </a:stretch>
-          </xdr:blipFill>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="451597" y="6858001"/>
-              <a:ext cx="8644442" cy="6707163"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-          </xdr:spPr>
-        </xdr:pic>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="5" name="正方形/長方形 4">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{29621CEE-FFA9-41F2-82FE-BB4DCB2E04BF}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="787025" y="7382434"/>
-              <a:ext cx="6298826" cy="663390"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln w="19050">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="2">
-              <a:schemeClr val="accent1">
-                <a:shade val="15000"/>
-              </a:schemeClr>
-            </a:lnRef>
-            <a:fillRef idx="1">
-              <a:schemeClr val="accent1"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:schemeClr val="accent1"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="lt1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-              <a:prstTxWarp prst="textNoShape">
-                <a:avLst/>
-              </a:prstTxWarp>
-              <a:noAutofit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="6" name="正方形/長方形 5">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4802FD5E-3434-4F4F-B126-1A203607A5F6}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="787025" y="8205694"/>
-              <a:ext cx="6298826" cy="663389"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln w="19050">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="2">
-              <a:schemeClr val="accent1">
-                <a:shade val="15000"/>
-              </a:schemeClr>
-            </a:lnRef>
-            <a:fillRef idx="1">
-              <a:schemeClr val="accent1"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:schemeClr val="accent1"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="lt1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-              <a:prstTxWarp prst="textNoShape">
-                <a:avLst/>
-              </a:prstTxWarp>
-              <a:noAutofit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="7" name="正方形/長方形 6">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F0BC66A4-C91E-4540-B454-FE4E7EBA9384}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="787025" y="9003553"/>
-              <a:ext cx="6298826" cy="663389"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln w="19050">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="2">
-              <a:schemeClr val="accent1">
-                <a:shade val="15000"/>
-              </a:schemeClr>
-            </a:lnRef>
-            <a:fillRef idx="1">
-              <a:schemeClr val="accent1"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:schemeClr val="accent1"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="lt1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-              <a:prstTxWarp prst="textNoShape">
-                <a:avLst/>
-              </a:prstTxWarp>
-              <a:noAutofit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="8" name="正方形/長方形 7">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E4824648-458C-47E0-974A-250D168D6FFA}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="787025" y="9780494"/>
-              <a:ext cx="7410450" cy="1296895"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln w="19050">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="2">
-              <a:schemeClr val="accent1">
-                <a:shade val="15000"/>
-              </a:schemeClr>
-            </a:lnRef>
-            <a:fillRef idx="1">
-              <a:schemeClr val="accent1"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:schemeClr val="accent1"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="lt1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-              <a:prstTxWarp prst="textNoShape">
-                <a:avLst/>
-              </a:prstTxWarp>
-              <a:noAutofit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="9" name="正方形/長方形 8">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2090D758-D61B-4F52-A10E-4475FD462964}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="787025" y="11189448"/>
-              <a:ext cx="7913594" cy="1364128"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln w="19050">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="2">
-              <a:schemeClr val="accent1">
-                <a:shade val="15000"/>
-              </a:schemeClr>
-            </a:lnRef>
-            <a:fillRef idx="1">
-              <a:schemeClr val="accent1"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:schemeClr val="accent1"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="lt1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-              <a:prstTxWarp prst="textNoShape">
-                <a:avLst/>
-              </a:prstTxWarp>
-              <a:noAutofit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </xdr:grpSp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="11" name="四角形: 角を丸くする 10">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D77BDC50-F2F2-4CB2-B3D2-EAE2344C5299}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="7220324" y="7581153"/>
-            <a:ext cx="470917" cy="266265"/>
-          </a:xfrm>
-          <a:prstGeom prst="roundRect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="FFFF00"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>①</a:t>
-            </a:r>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="12" name="四角形: 角を丸くする 11">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D55B315F-BD09-47D8-8720-5E9DDE316583}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="7220324" y="8495554"/>
-            <a:ext cx="470918" cy="266265"/>
-          </a:xfrm>
-          <a:prstGeom prst="roundRect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="FFFF00"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>②</a:t>
-            </a:r>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="13" name="四角形: 角を丸くする 12">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F6B0299-F035-4B3E-99E7-4EBFE16CFCED}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="7220324" y="9211237"/>
-            <a:ext cx="478014" cy="266264"/>
-          </a:xfrm>
-          <a:prstGeom prst="roundRect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="FFFF00"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>③</a:t>
-            </a:r>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="14" name="四角形: 角を丸くする 13">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07D4D0FD-B86B-44F2-B2CA-292F3455DC47}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="7455275" y="9874625"/>
-            <a:ext cx="478014" cy="266265"/>
-          </a:xfrm>
-          <a:prstGeom prst="roundRect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="FFFF00"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>④</a:t>
-            </a:r>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="15" name="四角形: 角を丸くする 14">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F9105148-1896-4AA4-C3EB-5C5A70F16E63}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="7462745" y="11246223"/>
-            <a:ext cx="478014" cy="266265"/>
-          </a:xfrm>
-          <a:prstGeom prst="roundRect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="FFFF00"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>⑤</a:t>
-            </a:r>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="16" name="四角形: 角を丸くする 15">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D4F7E7E-BA21-407E-B984-BCE4C8571DFA}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="5060950" y="10058401"/>
-            <a:ext cx="600262" cy="251011"/>
-          </a:xfrm>
-          <a:prstGeom prst="roundRect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="FFFF00"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>④</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>-1</a:t>
-            </a:r>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
-              </a:solidFill>
-            </a:endParaRPr>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="17" name="四角形: 角を丸くする 16">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A220A076-6F36-C78A-A41F-E8214C72A84F}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="5060950" y="10395324"/>
-            <a:ext cx="600262" cy="251012"/>
-          </a:xfrm>
-          <a:prstGeom prst="roundRect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="FFFF00"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>④</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>-2</a:t>
-            </a:r>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
-              </a:solidFill>
-            </a:endParaRPr>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="18" name="四角形: 角を丸くする 17">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{01EC93E1-6D4A-1AE9-9C16-0FCFDF4B8CDA}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="5060950" y="10732248"/>
-            <a:ext cx="600262" cy="248024"/>
-          </a:xfrm>
-          <a:prstGeom prst="roundRect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="FFFF00"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>④</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>-3</a:t>
-            </a:r>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
-              </a:solidFill>
-            </a:endParaRPr>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>4975785</xdr:colOff>
-      <xdr:row>98</xdr:row>
-      <xdr:rowOff>137155</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="2" name="グループ化 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1514306F-DEF6-4458-908C-661F1CBD436D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="463176" y="19162059"/>
-          <a:ext cx="10750550" cy="5695272"/>
-          <a:chOff x="647700" y="457199"/>
-          <a:chExt cx="10801350" cy="5620566"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="20" name="図 19">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF5FD2A7-BE53-2241-4B25-3D318FFC4DC5}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="660400" y="457199"/>
-            <a:ext cx="5276850" cy="1979739"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="21" name="図 20">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D1C893E0-B4FA-7CC3-0BEA-9A3C2E421E2B}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="647700" y="2559050"/>
-            <a:ext cx="10801350" cy="3518715"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="22" name="正方形/長方形 21">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8EF20EB7-2096-B49A-6A4A-11FABA6886E3}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="762000" y="533400"/>
-            <a:ext cx="5004734" cy="519953"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="23" name="正方形/長方形 22">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B80492CF-0056-38C1-120A-29F3DBEEA697}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="762000" y="1206500"/>
-            <a:ext cx="5016500" cy="519953"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="24" name="正方形/長方形 23">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{848EC580-6DF1-6D20-0DD9-DCD0F10EF1E9}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="762000" y="1860550"/>
-            <a:ext cx="5016500" cy="519953"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="25" name="正方形/長方形 24">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23179FEA-14FC-E3BE-A3F9-40B1CD9FA1B5}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="647700" y="3035301"/>
-            <a:ext cx="10750550" cy="298450"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="26" name="正方形/長方形 25">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{162BC2D1-AE6C-7933-473C-D095073E4609}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="996950" y="4826000"/>
-            <a:ext cx="2508250" cy="1225550"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="27" name="正方形/長方形 26">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6C2134E2-F284-235C-7550-EDC98B33CD1B}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="4146550" y="4006850"/>
-            <a:ext cx="3746500" cy="596900"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:cxnSp macro="">
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="28" name="コネクタ: カギ線 27">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C50F1A25-6D2B-6ADC-ED85-0CEE6139C459}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvCxnSpPr>
-            <a:stCxn id="22" idx="3"/>
-            <a:endCxn id="25" idx="0"/>
-          </xdr:cNvCxnSpPr>
-        </xdr:nvCxnSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="5766734" y="793377"/>
-            <a:ext cx="256241" cy="2241924"/>
-          </a:xfrm>
-          <a:prstGeom prst="bentConnector2">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-            <a:tailEnd type="triangle"/>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:lnRef>
-          <a:fillRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="tx1"/>
-          </a:fontRef>
-        </xdr:style>
-      </xdr:cxnSp>
-      <xdr:cxnSp macro="">
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="29" name="コネクタ: カギ線 28">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F68FFC1D-D82C-A634-4A1C-A4D77A9A5283}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvCxnSpPr>
-            <a:stCxn id="23" idx="1"/>
-            <a:endCxn id="26" idx="1"/>
-          </xdr:cNvCxnSpPr>
-        </xdr:nvCxnSpPr>
-        <xdr:spPr>
-          <a:xfrm rot="10800000" flipH="1" flipV="1">
-            <a:off x="762000" y="1466477"/>
-            <a:ext cx="234950" cy="3972298"/>
-          </a:xfrm>
-          <a:prstGeom prst="bentConnector3">
-            <a:avLst>
-              <a:gd name="adj1" fmla="val -97297"/>
-            </a:avLst>
-          </a:prstGeom>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-            <a:tailEnd type="triangle"/>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:lnRef>
-          <a:fillRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="tx1"/>
-          </a:fontRef>
-        </xdr:style>
-      </xdr:cxnSp>
-      <xdr:cxnSp macro="">
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="30" name="コネクタ: カギ線 29">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D2F9BCEC-33E9-56AE-D58B-1737A36BB400}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvCxnSpPr>
-            <a:stCxn id="24" idx="2"/>
-            <a:endCxn id="27" idx="0"/>
-          </xdr:cNvCxnSpPr>
-        </xdr:nvCxnSpPr>
-        <xdr:spPr>
-          <a:xfrm rot="16200000" flipH="1">
-            <a:off x="3831852" y="1818901"/>
-            <a:ext cx="1626347" cy="2749550"/>
-          </a:xfrm>
-          <a:prstGeom prst="bentConnector3">
-            <a:avLst>
-              <a:gd name="adj1" fmla="val 76160"/>
-            </a:avLst>
-          </a:prstGeom>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-            <a:tailEnd type="triangle"/>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:lnRef>
-          <a:fillRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="tx1"/>
-          </a:fontRef>
-        </xdr:style>
-      </xdr:cxnSp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>14942</xdr:colOff>
       <xdr:row>105</xdr:row>
@@ -3149,7 +1668,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3192,8 +1711,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="485588" y="30143823"/>
-          <a:ext cx="8637345" cy="1813430"/>
+          <a:off x="501383" y="29815117"/>
+          <a:ext cx="8642895" cy="1789524"/>
           <a:chOff x="469900" y="29032200"/>
           <a:chExt cx="8641080" cy="1792512"/>
         </a:xfrm>
@@ -3212,7 +1731,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -3386,6 +1905,1634 @@
     </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>4975785</xdr:colOff>
+      <xdr:row>98</xdr:row>
+      <xdr:rowOff>137155</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="37" name="グループ化 36">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E0660B31-C97F-6385-E876-1F382E645AEE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="478971" y="18973800"/>
+          <a:ext cx="10756100" cy="5623555"/>
+          <a:chOff x="472440" y="18973800"/>
+          <a:chExt cx="10751745" cy="5623555"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="2" name="グループ化 1">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1514306F-DEF6-4458-908C-661F1CBD436D}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="472440" y="18973800"/>
+            <a:ext cx="10751745" cy="5623555"/>
+            <a:chOff x="647700" y="457199"/>
+            <a:chExt cx="10801350" cy="5620566"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="20" name="図 19">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF5FD2A7-BE53-2241-4B25-3D318FFC4DC5}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="660400" y="457199"/>
+              <a:ext cx="5276850" cy="1979739"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="21" name="図 20">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D1C893E0-B4FA-7CC3-0BEA-9A3C2E421E2B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="647700" y="2559050"/>
+              <a:ext cx="10801350" cy="3518715"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="22" name="正方形/長方形 21">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8EF20EB7-2096-B49A-6A4A-11FABA6886E3}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="762000" y="533400"/>
+              <a:ext cx="5004734" cy="519953"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="23" name="正方形/長方形 22">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B80492CF-0056-38C1-120A-29F3DBEEA697}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="762000" y="1206500"/>
+              <a:ext cx="5016500" cy="519953"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="24" name="正方形/長方形 23">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{848EC580-6DF1-6D20-0DD9-DCD0F10EF1E9}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="762000" y="1860550"/>
+              <a:ext cx="5016500" cy="519953"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="25" name="正方形/長方形 24">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23179FEA-14FC-E3BE-A3F9-40B1CD9FA1B5}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="647700" y="3035301"/>
+              <a:ext cx="10750550" cy="298450"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="26" name="正方形/長方形 25">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{162BC2D1-AE6C-7933-473C-D095073E4609}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="996950" y="4826000"/>
+              <a:ext cx="2508250" cy="1225550"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="27" name="正方形/長方形 26">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6C2134E2-F284-235C-7550-EDC98B33CD1B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4146550" y="4006850"/>
+              <a:ext cx="3746500" cy="596900"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="28" name="コネクタ: カギ線 27">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C50F1A25-6D2B-6ADC-ED85-0CEE6139C459}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr>
+              <a:stCxn id="22" idx="3"/>
+              <a:endCxn id="25" idx="0"/>
+            </xdr:cNvCxnSpPr>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5766734" y="793377"/>
+              <a:ext cx="256241" cy="2241924"/>
+            </a:xfrm>
+            <a:prstGeom prst="bentConnector2">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:tailEnd type="triangle"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="29" name="コネクタ: カギ線 28">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F68FFC1D-D82C-A634-4A1C-A4D77A9A5283}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr>
+              <a:stCxn id="23" idx="1"/>
+              <a:endCxn id="26" idx="1"/>
+            </xdr:cNvCxnSpPr>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm rot="10800000" flipH="1" flipV="1">
+              <a:off x="762000" y="1466477"/>
+              <a:ext cx="234950" cy="3972298"/>
+            </a:xfrm>
+            <a:prstGeom prst="bentConnector3">
+              <a:avLst>
+                <a:gd name="adj1" fmla="val -97297"/>
+              </a:avLst>
+            </a:prstGeom>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:tailEnd type="triangle"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="30" name="コネクタ: カギ線 29">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D2F9BCEC-33E9-56AE-D58B-1737A36BB400}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr>
+              <a:stCxn id="24" idx="2"/>
+              <a:endCxn id="27" idx="0"/>
+            </xdr:cNvCxnSpPr>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm rot="16200000" flipH="1">
+              <a:off x="3831852" y="1818901"/>
+              <a:ext cx="1626347" cy="2749550"/>
+            </a:xfrm>
+            <a:prstGeom prst="bentConnector3">
+              <a:avLst>
+                <a:gd name="adj1" fmla="val 76160"/>
+              </a:avLst>
+            </a:prstGeom>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:tailEnd type="triangle"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+      </xdr:grpSp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="31" name="図 30">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E105AC68-4A10-49C7-8D21-079C2550E838}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="490369" y="21102917"/>
+            <a:ext cx="250353" cy="221456"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>234790</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>18143</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>2748494</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>95906</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="40" name="グループ化 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AEB125AA-3730-8478-78D7-2C0A55876C8A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="474276" y="6418943"/>
+          <a:ext cx="8533504" cy="6707163"/>
+          <a:chOff x="471010" y="6418943"/>
+          <a:chExt cx="8525884" cy="6707163"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="19" name="グループ化 18">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FA50BCC8-2454-350D-91C4-3142E4A93BAC}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="471010" y="6418943"/>
+            <a:ext cx="8525884" cy="6707163"/>
+            <a:chOff x="451597" y="6858001"/>
+            <a:chExt cx="8644442" cy="6707163"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:grpSp>
+          <xdr:nvGrpSpPr>
+            <xdr:cNvPr id="10" name="グループ化 9">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F9C3B10C-11A3-2DA9-9315-B4A472E94991}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGrpSpPr/>
+          </xdr:nvGrpSpPr>
+          <xdr:grpSpPr>
+            <a:xfrm>
+              <a:off x="451597" y="6858001"/>
+              <a:ext cx="8644442" cy="6707163"/>
+              <a:chOff x="451597" y="6858001"/>
+              <a:chExt cx="8644442" cy="6707163"/>
+            </a:xfrm>
+          </xdr:grpSpPr>
+          <xdr:pic>
+            <xdr:nvPicPr>
+              <xdr:cNvPr id="4" name="図 3">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5692D72E-F8A2-7504-97D3-F475AD699425}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvPicPr>
+                <a:picLocks noChangeAspect="1"/>
+              </xdr:cNvPicPr>
+            </xdr:nvPicPr>
+            <xdr:blipFill>
+              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+              <a:stretch>
+                <a:fillRect/>
+              </a:stretch>
+            </xdr:blipFill>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="451597" y="6858001"/>
+                <a:ext cx="8644442" cy="6707163"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+            </xdr:spPr>
+          </xdr:pic>
+          <xdr:sp macro="" textlink="">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="5" name="正方形/長方形 4">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{29621CEE-FFA9-41F2-82FE-BB4DCB2E04BF}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvSpPr/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="787025" y="7382434"/>
+                <a:ext cx="6298826" cy="663390"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="2">
+                <a:schemeClr val="accent1">
+                  <a:shade val="15000"/>
+                </a:schemeClr>
+              </a:lnRef>
+              <a:fillRef idx="1">
+                <a:schemeClr val="accent1"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:schemeClr val="accent1"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="lt1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+                <a:prstTxWarp prst="textNoShape">
+                  <a:avLst/>
+                </a:prstTxWarp>
+                <a:noAutofit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+          <xdr:sp macro="" textlink="">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="6" name="正方形/長方形 5">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4802FD5E-3434-4F4F-B126-1A203607A5F6}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvSpPr/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="787025" y="8205694"/>
+                <a:ext cx="6298826" cy="663389"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="2">
+                <a:schemeClr val="accent1">
+                  <a:shade val="15000"/>
+                </a:schemeClr>
+              </a:lnRef>
+              <a:fillRef idx="1">
+                <a:schemeClr val="accent1"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:schemeClr val="accent1"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="lt1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+                <a:prstTxWarp prst="textNoShape">
+                  <a:avLst/>
+                </a:prstTxWarp>
+                <a:noAutofit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+          <xdr:sp macro="" textlink="">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="7" name="正方形/長方形 6">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F0BC66A4-C91E-4540-B454-FE4E7EBA9384}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvSpPr/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="787025" y="9003553"/>
+                <a:ext cx="6298826" cy="663389"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="2">
+                <a:schemeClr val="accent1">
+                  <a:shade val="15000"/>
+                </a:schemeClr>
+              </a:lnRef>
+              <a:fillRef idx="1">
+                <a:schemeClr val="accent1"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:schemeClr val="accent1"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="lt1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+                <a:prstTxWarp prst="textNoShape">
+                  <a:avLst/>
+                </a:prstTxWarp>
+                <a:noAutofit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+          <xdr:sp macro="" textlink="">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="8" name="正方形/長方形 7">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E4824648-458C-47E0-974A-250D168D6FFA}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvSpPr/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="787025" y="9780494"/>
+                <a:ext cx="7410450" cy="1296895"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="2">
+                <a:schemeClr val="accent1">
+                  <a:shade val="15000"/>
+                </a:schemeClr>
+              </a:lnRef>
+              <a:fillRef idx="1">
+                <a:schemeClr val="accent1"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:schemeClr val="accent1"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="lt1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+                <a:prstTxWarp prst="textNoShape">
+                  <a:avLst/>
+                </a:prstTxWarp>
+                <a:noAutofit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+          <xdr:sp macro="" textlink="">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="9" name="正方形/長方形 8">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2090D758-D61B-4F52-A10E-4475FD462964}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvSpPr/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="787025" y="11189448"/>
+                <a:ext cx="7913594" cy="1364128"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="2">
+                <a:schemeClr val="accent1">
+                  <a:shade val="15000"/>
+                </a:schemeClr>
+              </a:lnRef>
+              <a:fillRef idx="1">
+                <a:schemeClr val="accent1"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:schemeClr val="accent1"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="lt1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+                <a:prstTxWarp prst="textNoShape">
+                  <a:avLst/>
+                </a:prstTxWarp>
+                <a:noAutofit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+        </xdr:grpSp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="11" name="四角形: 角を丸くする 10">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D77BDC50-F2F2-4CB2-B3D2-EAE2344C5299}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7220324" y="7581153"/>
+              <a:ext cx="470917" cy="266265"/>
+            </a:xfrm>
+            <a:prstGeom prst="roundRect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
+            </a:solidFill>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>①</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="12" name="四角形: 角を丸くする 11">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D55B315F-BD09-47D8-8720-5E9DDE316583}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7220324" y="8495554"/>
+              <a:ext cx="470918" cy="266265"/>
+            </a:xfrm>
+            <a:prstGeom prst="roundRect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
+            </a:solidFill>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>②</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="13" name="四角形: 角を丸くする 12">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F6B0299-F035-4B3E-99E7-4EBFE16CFCED}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7220324" y="9211237"/>
+              <a:ext cx="478014" cy="266264"/>
+            </a:xfrm>
+            <a:prstGeom prst="roundRect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
+            </a:solidFill>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>③</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="14" name="四角形: 角を丸くする 13">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07D4D0FD-B86B-44F2-B2CA-292F3455DC47}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7455275" y="9874625"/>
+              <a:ext cx="478014" cy="266265"/>
+            </a:xfrm>
+            <a:prstGeom prst="roundRect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
+            </a:solidFill>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>④</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="15" name="四角形: 角を丸くする 14">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F9105148-1896-4AA4-C3EB-5C5A70F16E63}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7462745" y="11246223"/>
+              <a:ext cx="478014" cy="266265"/>
+            </a:xfrm>
+            <a:prstGeom prst="roundRect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
+            </a:solidFill>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>⑤</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="16" name="四角形: 角を丸くする 15">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D4F7E7E-BA21-407E-B984-BCE4C8571DFA}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5060950" y="10058401"/>
+              <a:ext cx="600262" cy="251011"/>
+            </a:xfrm>
+            <a:prstGeom prst="roundRect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
+            </a:solidFill>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>④</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>-1</a:t>
+              </a:r>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+              </a:endParaRPr>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="17" name="四角形: 角を丸くする 16">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A220A076-6F36-C78A-A41F-E8214C72A84F}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5060950" y="10395324"/>
+              <a:ext cx="600262" cy="251012"/>
+            </a:xfrm>
+            <a:prstGeom prst="roundRect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
+            </a:solidFill>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>④</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>-2</a:t>
+              </a:r>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+              </a:endParaRPr>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="18" name="四角形: 角を丸くする 17">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{01EC93E1-6D4A-1AE9-9C16-0FCFDF4B8CDA}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5060950" y="10732248"/>
+              <a:ext cx="600262" cy="248024"/>
+            </a:xfrm>
+            <a:prstGeom prst="roundRect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
+            </a:solidFill>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>④</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>-3</a:t>
+              </a:r>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+              </a:endParaRPr>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="38" name="図 37">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9D78934-7805-431A-BAE8-F3CA69B8F498}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="553122" y="6499412"/>
+            <a:ext cx="277788" cy="246530"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>231587</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>216647</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>2745291</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>148091</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="42" name="グループ化 41">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{37F43019-F499-6A32-FAF4-F4C2A7A0A4A8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="471073" y="2045447"/>
+          <a:ext cx="8533504" cy="3131844"/>
+          <a:chOff x="467807" y="2045447"/>
+          <a:chExt cx="8525884" cy="3131844"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="3" name="図 2">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{38322839-826B-DCA2-2B93-6D1E32875A01}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="467807" y="2045447"/>
+            <a:ext cx="8525884" cy="3131844"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="41" name="図 40">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC6747DA-F1C6-42E9-9E85-A8A7E5522F9E}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="535192" y="2111188"/>
+            <a:ext cx="326833" cy="282388"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -3417,8 +3564,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="647700" y="460187"/>
-          <a:ext cx="10750550" cy="5695272"/>
+          <a:off x="647700" y="461681"/>
+          <a:ext cx="11004550" cy="5732625"/>
           <a:chOff x="647700" y="457199"/>
           <a:chExt cx="10801350" cy="5620566"/>
         </a:xfrm>
@@ -3981,8 +4128,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="691776" y="743448"/>
-          <a:ext cx="6056033" cy="5032687"/>
+          <a:off x="694765" y="747930"/>
+          <a:ext cx="6096373" cy="5064063"/>
           <a:chOff x="698500" y="436033"/>
           <a:chExt cx="6146800" cy="4969934"/>
         </a:xfrm>
@@ -6183,8 +6330,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="254000" y="7933766"/>
-          <a:ext cx="8520057" cy="6579719"/>
+          <a:off x="255494" y="7984566"/>
+          <a:ext cx="8573845" cy="6621554"/>
           <a:chOff x="234950" y="6400801"/>
           <a:chExt cx="8641080" cy="6496049"/>
         </a:xfrm>
@@ -6447,8 +6594,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="231588" y="15583649"/>
-          <a:ext cx="8520057" cy="5343485"/>
+          <a:off x="233082" y="15683755"/>
+          <a:ext cx="8573845" cy="5377850"/>
           <a:chOff x="234950" y="14240437"/>
           <a:chExt cx="8641080" cy="5274756"/>
         </a:xfrm>
@@ -6887,8 +7034,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="231588" y="67464747"/>
-          <a:ext cx="10650071" cy="8259649"/>
+          <a:off x="233082" y="67899536"/>
+          <a:ext cx="10717306" cy="8311942"/>
           <a:chOff x="217714" y="64949614"/>
           <a:chExt cx="10800443" cy="8155060"/>
         </a:xfrm>
@@ -7052,8 +7199,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="231588" y="58396522"/>
-          <a:ext cx="10650071" cy="7946338"/>
+          <a:off x="233082" y="58773040"/>
+          <a:ext cx="10717306" cy="7997138"/>
           <a:chOff x="234950" y="56500487"/>
           <a:chExt cx="10801350" cy="7844738"/>
         </a:xfrm>
@@ -7330,8 +7477,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="240658" y="77219466"/>
-          <a:ext cx="10645802" cy="6857194"/>
+          <a:off x="242152" y="77717008"/>
+          <a:ext cx="10714532" cy="6902017"/>
           <a:chOff x="226785" y="75309984"/>
           <a:chExt cx="10800443" cy="6767548"/>
         </a:xfrm>
@@ -7661,8 +7808,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9039410" y="1579284"/>
-          <a:ext cx="6060968" cy="3673815"/>
+          <a:off x="9097681" y="1588249"/>
+          <a:ext cx="6099815" cy="3697721"/>
           <a:chOff x="9170519" y="1561355"/>
           <a:chExt cx="6148374" cy="3626328"/>
         </a:xfrm>
@@ -9092,8 +9239,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="18534529" y="1875117"/>
-          <a:ext cx="4176059" cy="5353423"/>
+          <a:off x="18654058" y="1887070"/>
+          <a:ext cx="4202954" cy="5387788"/>
           <a:chOff x="18810940" y="1513541"/>
           <a:chExt cx="4236571" cy="5284693"/>
         </a:xfrm>
@@ -10396,8 +10543,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="249731" y="89474701"/>
-          <a:ext cx="10645802" cy="6853188"/>
+          <a:off x="251225" y="90051430"/>
+          <a:ext cx="10714532" cy="6896517"/>
           <a:chOff x="253093" y="88321242"/>
           <a:chExt cx="10800443" cy="6766529"/>
         </a:xfrm>
@@ -10515,8 +10662,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="249731" y="97571218"/>
-          <a:ext cx="10645802" cy="6853190"/>
+          <a:off x="251225" y="98200242"/>
+          <a:ext cx="10714532" cy="6896519"/>
           <a:chOff x="253093" y="96313171"/>
           <a:chExt cx="10800443" cy="6766531"/>
         </a:xfrm>
@@ -10875,16 +11022,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{247D8D20-CE8B-4D82-A6C6-EA8B8BD03E4C}">
   <dimension ref="A2:G578"/>
-  <sheetFormatPr defaultColWidth="3.08203125" defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="3.09765625" defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="4" width="3.08203125" style="1"/>
-    <col min="5" max="5" width="6.9140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="62.75" style="1" customWidth="1"/>
-    <col min="7" max="7" width="87.6640625" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="3.08203125" style="1"/>
+    <col min="1" max="4" width="3.09765625" style="1"/>
+    <col min="5" max="5" width="6.8984375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="62.69921875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="87.69921875" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="3.09765625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -10892,37 +11039,37 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B3" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B4" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B5" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B6" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B7" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B8" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A25" s="1" t="s">
         <v>0</v>
       </c>
@@ -10930,23 +11077,23 @@
         <v>53</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B26" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B27" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B33" s="2"/>
     </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B42" s="2"/>
     </row>
-    <row r="60" spans="5:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="5:7" x14ac:dyDescent="0.45">
       <c r="E60" s="6" t="s">
         <v>57</v>
       </c>
@@ -10957,7 +11104,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="5:7" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="5:7" ht="36" x14ac:dyDescent="0.45">
       <c r="E61" s="5" t="s">
         <v>60</v>
       </c>
@@ -10968,7 +11115,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="62" spans="5:7" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="5:7" ht="36" x14ac:dyDescent="0.45">
       <c r="E62" s="5" t="s">
         <v>61</v>
       </c>
@@ -10979,7 +11126,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="63" spans="5:7" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="5:7" ht="36" x14ac:dyDescent="0.45">
       <c r="E63" s="5" t="s">
         <v>62</v>
       </c>
@@ -10990,7 +11137,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="64" spans="5:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="5:7" x14ac:dyDescent="0.45">
       <c r="E64" s="5" t="s">
         <v>63</v>
       </c>
@@ -11001,7 +11148,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:7" ht="36" x14ac:dyDescent="0.45">
       <c r="B65" s="2"/>
       <c r="E65" s="5" t="s">
         <v>64</v>
@@ -11013,7 +11160,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:7" ht="36" x14ac:dyDescent="0.45">
       <c r="E66" s="5" t="s">
         <v>65</v>
       </c>
@@ -11024,7 +11171,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:7" ht="36" x14ac:dyDescent="0.45">
       <c r="E67" s="5" t="s">
         <v>66</v>
       </c>
@@ -11035,7 +11182,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="72" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:7" ht="72" x14ac:dyDescent="0.45">
       <c r="E68" s="5" t="s">
         <v>67</v>
       </c>
@@ -11046,12 +11193,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.45">
       <c r="E69" s="4"/>
       <c r="F69" s="4"/>
       <c r="G69" s="4"/>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A71" s="1" t="s">
         <v>0</v>
       </c>
@@ -11059,26 +11206,26 @@
         <v>85</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B72" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.45">
       <c r="B73" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.45">
       <c r="D75"/>
     </row>
-    <row r="87" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B87" s="2"/>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B97" s="2"/>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A102" s="1" t="s">
         <v>0</v>
       </c>
@@ -11086,20 +11233,20 @@
         <v>86</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B103" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B104" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B111" s="2"/>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A116" s="1" t="s">
         <v>0</v>
       </c>
@@ -11107,102 +11254,102 @@
         <v>89</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B117" s="1" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B118" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B119" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B120" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="135" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="135" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B135" s="2"/>
     </row>
-    <row r="150" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="150" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B150" s="2"/>
     </row>
-    <row r="169" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="169" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B169" s="2"/>
     </row>
-    <row r="173" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="173" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B173" s="2"/>
     </row>
-    <row r="188" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="188" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B188" s="2"/>
     </row>
-    <row r="208" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="208" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B208" s="2"/>
     </row>
-    <row r="227" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="227" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B227" s="2"/>
     </row>
-    <row r="241" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="241" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B241" s="2"/>
     </row>
-    <row r="254" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="254" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B254" s="2"/>
     </row>
-    <row r="263" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="263" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B263" s="2"/>
     </row>
-    <row r="282" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="282" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B282" s="2"/>
     </row>
-    <row r="294" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="294" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B294" s="2"/>
     </row>
-    <row r="306" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="306" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B306" s="2"/>
     </row>
-    <row r="335" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="335" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B335" s="2"/>
     </row>
-    <row r="338" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="338" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B338" s="3"/>
     </row>
-    <row r="361" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="361" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B361" s="2"/>
     </row>
-    <row r="370" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="370" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B370" s="2"/>
     </row>
-    <row r="388" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="388" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B388" s="2"/>
     </row>
-    <row r="389" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="389" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B389" s="2"/>
     </row>
-    <row r="415" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="415" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B415" s="2"/>
     </row>
-    <row r="424" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="424" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B424" s="2"/>
     </row>
-    <row r="441" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="441" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B441" s="2"/>
     </row>
-    <row r="474" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="474" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B474" s="2"/>
     </row>
-    <row r="516" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="516" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B516" s="2"/>
     </row>
-    <row r="543" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="543" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B543" s="2"/>
     </row>
-    <row r="578" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="578" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B578" s="2"/>
     </row>
   </sheetData>
@@ -11215,7 +11362,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E043A0C8-F566-4C43-B1C1-68D829264C9A}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <sheetData/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11226,12 +11373,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A29FA320-DA47-41A9-9EA7-7E68689E0E1F}">
   <dimension ref="A1:ED573"/>
-  <sheetFormatPr defaultColWidth="3.08203125" defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="3.09765625" defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="16384" width="3.08203125" style="1"/>
+    <col min="1" max="16384" width="3.09765625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:134" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:134" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>38</v>
       </c>
@@ -11629,7 +11776,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:134" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:134" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -11649,7 +11796,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:134" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:134" x14ac:dyDescent="0.45">
       <c r="AN4" s="1" t="s">
         <v>40</v>
       </c>
@@ -11657,7 +11804,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:134" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:134" x14ac:dyDescent="0.45">
       <c r="AN5" s="1" t="s">
         <v>37</v>
       </c>
@@ -11665,7 +11812,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:134" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:134" x14ac:dyDescent="0.45">
       <c r="AN6" s="1" t="s">
         <v>41</v>
       </c>
@@ -11673,12 +11820,12 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:134" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:134" x14ac:dyDescent="0.45">
       <c r="CD7" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A33" s="1" t="s">
         <v>0</v>
       </c>
@@ -11686,15 +11833,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B34" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B42" s="2"/>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A65" s="1" t="s">
         <v>0</v>
       </c>
@@ -11702,20 +11849,20 @@
         <v>4</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B66" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B67" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B82" s="2"/>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A92" s="1" t="s">
         <v>0</v>
       </c>
@@ -11723,15 +11870,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B93" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="106" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="106" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B106" s="2"/>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A130" s="1" t="s">
         <v>0</v>
       </c>
@@ -11739,18 +11886,18 @@
         <v>8</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B131" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="145" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="145" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B145" s="2"/>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="164" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B164" s="2"/>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="168" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A168" s="1" t="s">
         <v>0</v>
       </c>
@@ -11758,12 +11905,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="169" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B169" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="183" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A183" s="1" t="s">
         <v>0</v>
       </c>
@@ -11771,20 +11918,20 @@
         <v>12</v>
       </c>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="184" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B184" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="185" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B185" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="203" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="203" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B203" s="2"/>
     </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="222" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A222" s="1" t="s">
         <v>0</v>
       </c>
@@ -11792,20 +11939,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="223" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B223" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="224" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B224" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="236" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="236" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B236" s="2"/>
     </row>
-    <row r="249" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="249" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A249" s="1" t="s">
         <v>0</v>
       </c>
@@ -11813,28 +11960,28 @@
         <v>18</v>
       </c>
     </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="250" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B250" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="251" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B251" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="252" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="252" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B252" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="258" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="258" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B258" s="2"/>
     </row>
-    <row r="277" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="277" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B277" s="2"/>
     </row>
-    <row r="289" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="289" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A289" s="1" t="s">
         <v>0</v>
       </c>
@@ -11842,20 +11989,20 @@
         <v>21</v>
       </c>
     </row>
-    <row r="290" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="290" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B290" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="291" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="291" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B291" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="301" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="301" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B301" s="2"/>
     </row>
-    <row r="330" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="330" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A330" s="1" t="s">
         <v>0</v>
       </c>
@@ -11863,25 +12010,25 @@
         <v>25</v>
       </c>
     </row>
-    <row r="331" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="331" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B331" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="332" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="332" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B332" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="333" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="333" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B333" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="356" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="356" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B356" s="2"/>
     </row>
-    <row r="365" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="365" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A365" s="1" t="s">
         <v>0</v>
       </c>
@@ -11889,15 +12036,15 @@
         <v>29</v>
       </c>
     </row>
-    <row r="366" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="366" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B366" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="383" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="383" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B383" s="2"/>
     </row>
-    <row r="384" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="384" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A384" s="1" t="s">
         <v>0</v>
       </c>
@@ -11905,20 +12052,20 @@
         <v>30</v>
       </c>
     </row>
-    <row r="385" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="385" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B385" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="386" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="386" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B386" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="410" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="410" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B410" s="2"/>
     </row>
-    <row r="419" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="419" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A419" s="1" t="s">
         <v>0</v>
       </c>
@@ -11926,29 +12073,29 @@
         <v>33</v>
       </c>
     </row>
-    <row r="420" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="420" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B420" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="421" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="421" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B421" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="436" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="436" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B436" s="2"/>
     </row>
-    <row r="469" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="469" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B469" s="2"/>
     </row>
-    <row r="511" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="511" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B511" s="2"/>
     </row>
-    <row r="538" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="538" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B538" s="2"/>
     </row>
-    <row r="573" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="573" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B573" s="2"/>
     </row>
   </sheetData>
